--- a/tables/model_summaries.xlsx
+++ b/tables/model_summaries.xlsx
@@ -12,8 +12,7 @@
     <sheet name="PAH" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="PCP" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="POP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Pesticide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Plasticizer" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Plasticizer" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -465,16 +464,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2467</v>
+        <v>1.3554</v>
       </c>
       <c r="C2" t="n">
-        <v>85835.7724</v>
+        <v>25196.7962</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2798</v>
+        <v>3.8783</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -488,22 +487,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2594</v>
+        <v>-0.2741</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2233</v>
+        <v>0.2489</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2453</v>
+        <v>0.2708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7715</v>
+        <v>0.7603</v>
       </c>
       <c r="F3" t="n">
-        <v>0.498</v>
+        <v>0.4668</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1951</v>
+        <v>1.2382</v>
       </c>
     </row>
     <row r="4">
@@ -511,22 +510,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.1332</v>
+        <v>-0.1467</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1692</v>
+        <v>0.1799</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4313</v>
+        <v>0.4146</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8753</v>
+        <v>0.8635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6283</v>
+        <v>0.607</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2195</v>
+        <v>1.2285</v>
       </c>
     </row>
     <row r="5">
@@ -534,16 +533,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.7446</v>
+        <v>1.692</v>
       </c>
       <c r="C5" t="n">
-        <v>85835.7724</v>
+        <v>25196.7962</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7236</v>
+        <v>5.4301</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -557,16 +556,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1.8241</v>
+        <v>1.8706</v>
       </c>
       <c r="C6" t="n">
-        <v>85835.7724</v>
+        <v>25196.7961</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1972</v>
+        <v>6.4922</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -606,16 +605,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>1.3493</v>
+        <v>1.2826</v>
       </c>
       <c r="C9" t="n">
-        <v>85835.7724</v>
+        <v>25196.7962</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8549</v>
+        <v>3.6058</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -655,22 +654,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.5778</v>
+        <v>-1.4384</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6369</v>
+        <v>1.7705</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3643</v>
+        <v>0.4165</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5611</v>
+        <v>0.2373</v>
       </c>
       <c r="F12" t="n">
-        <v>0.161</v>
+        <v>0.0074</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9553</v>
+        <v>7.6263</v>
       </c>
     </row>
     <row r="13">
@@ -678,22 +677,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.0665</v>
+        <v>-2.7614</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8657</v>
+        <v>2.259</v>
       </c>
       <c r="D13" t="n">
-        <v>0.218</v>
+        <v>0.2216</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3442</v>
+        <v>0.0632</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0631</v>
+        <v>0.0008</v>
       </c>
       <c r="G13" t="n">
-        <v>1.878</v>
+        <v>5.2921</v>
       </c>
     </row>
     <row r="14">
@@ -701,22 +700,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.2398</v>
+        <v>-3.4418</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8763</v>
+        <v>2.5887</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1571</v>
+        <v>0.1837</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2895</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="n">
-        <v>0.052</v>
+        <v>0.0002</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6125</v>
+        <v>5.114</v>
       </c>
     </row>
     <row r="15">
@@ -724,22 +723,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-1.1869</v>
+        <v>-3.4452</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8084</v>
+        <v>2.4488</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1421</v>
+        <v>0.1595</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3052</v>
+        <v>0.0319</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0626</v>
+        <v>0.0003</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4883</v>
+        <v>3.8741</v>
       </c>
     </row>
     <row r="16">
@@ -747,22 +746,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.0491</v>
+        <v>-2.776</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7556</v>
+        <v>1.9099</v>
       </c>
       <c r="D16" t="n">
-        <v>0.165</v>
+        <v>0.1461</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3503</v>
+        <v>0.0623</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0797</v>
+        <v>0.0015</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5401</v>
+        <v>2.6307</v>
       </c>
     </row>
     <row r="17">
@@ -770,22 +769,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.8321</v>
+        <v>-1.4673</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7133</v>
+        <v>1.7151</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2434</v>
+        <v>0.3923</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4351</v>
+        <v>0.2306</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1075</v>
+        <v>0.008</v>
       </c>
       <c r="G17" t="n">
-        <v>1.761</v>
+        <v>6.6471</v>
       </c>
     </row>
     <row r="18">
@@ -793,22 +792,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.7644</v>
+        <v>-1.6425</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6983</v>
+        <v>1.6961</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2736</v>
+        <v>0.3328</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4656</v>
+        <v>0.1935</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1185</v>
+        <v>0.007</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8297</v>
+        <v>5.3752</v>
       </c>
     </row>
     <row r="19">
@@ -816,22 +815,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.9932</v>
+        <v>-2.1876</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6979</v>
+        <v>1.6992</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1547</v>
+        <v>0.1979</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3704</v>
+        <v>0.1122</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0943</v>
+        <v>0.004</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4546</v>
+        <v>3.1355</v>
       </c>
     </row>
     <row r="20">
@@ -839,22 +838,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.1157</v>
+        <v>-1.9672</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7571</v>
+        <v>1.9567</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1406</v>
+        <v>0.3147</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3277</v>
+        <v>0.1398</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0743</v>
+        <v>0.003</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4452</v>
+        <v>6.4748</v>
       </c>
     </row>
     <row r="21">
@@ -862,22 +861,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.1348</v>
+        <v>-1.7608</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8509</v>
+        <v>3.3594</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1823</v>
+        <v>0.6002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3215</v>
+        <v>0.1719</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0607</v>
+        <v>0.0002</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7041</v>
+        <v>124.3964</v>
       </c>
     </row>
     <row r="22">
@@ -885,22 +884,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.1315</v>
+        <v>-1.5544</v>
       </c>
       <c r="C22" t="n">
-        <v>1.151</v>
+        <v>5.7426</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3256</v>
+        <v>0.7866</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3225</v>
+        <v>0.2113</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0338</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3.0786</v>
+        <v>16332.489</v>
       </c>
     </row>
     <row r="23">
@@ -908,22 +907,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.1283</v>
+        <v>-1.348</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7581</v>
+        <v>8.7542</v>
       </c>
       <c r="D23" t="n">
-        <v>0.521</v>
+        <v>0.8776</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3236</v>
+        <v>0.2598</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1497</v>
+        <v>7348009.0497</v>
       </c>
     </row>
     <row r="24">
@@ -931,22 +930,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.225</v>
+        <v>-1.3213</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2217</v>
+        <v>0.2772</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2938</v>
+        <v>0.2668</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1902</v>
+        <v>0.155</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4536</v>
+        <v>0.4593</v>
       </c>
     </row>
   </sheetData>
@@ -988,22 +987,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>2.6061</v>
+        <v>2.6967</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3602</v>
+        <v>0.3458</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>13.5462</v>
+        <v>14.8302</v>
       </c>
       <c r="F2" t="n">
-        <v>6.6873</v>
+        <v>7.5298</v>
       </c>
       <c r="G2" t="n">
-        <v>27.4403</v>
+        <v>29.2088</v>
       </c>
     </row>
     <row r="3">
@@ -1011,22 +1010,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1333</v>
+        <v>0.1538</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0922</v>
+        <v>0.0961</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1481</v>
+        <v>0.1093</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1426</v>
+        <v>1.1663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9538</v>
+        <v>0.9661</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3687</v>
+        <v>1.4079</v>
       </c>
     </row>
     <row r="4">
@@ -1034,22 +1033,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.051</v>
+        <v>-0.008</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0868</v>
+        <v>0.0964</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5572</v>
+        <v>0.9336</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0523</v>
+        <v>0.992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8876</v>
+        <v>0.8211</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2475</v>
+        <v>1.1984</v>
       </c>
     </row>
     <row r="5">
@@ -1057,22 +1056,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2528</v>
+        <v>-0.2287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1693</v>
+        <v>0.1554</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1354</v>
+        <v>0.141</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7766</v>
+        <v>0.7956</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5573</v>
+        <v>0.5867</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0823</v>
+        <v>1.0787</v>
       </c>
     </row>
     <row r="6">
@@ -1080,22 +1079,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2477</v>
+        <v>-0.0313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1551</v>
+        <v>0.1795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1103</v>
+        <v>0.8614</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2811</v>
+        <v>0.9691</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9453</v>
+        <v>0.6817</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7362</v>
+        <v>1.3779</v>
       </c>
     </row>
     <row r="7">
@@ -1103,22 +1102,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.5064</v>
+        <v>-0.5144</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2024</v>
+        <v>0.1936</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0124</v>
+        <v>0.0079</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6027</v>
+        <v>0.5979</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4053</v>
+        <v>0.409</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8962</v>
+        <v>0.8738</v>
       </c>
     </row>
     <row r="8">
@@ -1126,22 +1125,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>0.345</v>
+        <v>0.4054</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1549</v>
+        <v>0.2358</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0259</v>
+        <v>0.0855</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4119</v>
+        <v>1.4999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0422</v>
+        <v>0.9449</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9128</v>
+        <v>2.3809</v>
       </c>
     </row>
     <row r="9">
@@ -1149,22 +1148,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.3807</v>
+        <v>-0.3759</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2159</v>
+        <v>0.1956</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0778</v>
+        <v>0.0546</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6834</v>
+        <v>0.6867</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4476</v>
+        <v>0.468</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0433</v>
+        <v>1.0075</v>
       </c>
     </row>
     <row r="10">
@@ -1172,22 +1171,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2623</v>
+        <v>0.2224</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1473</v>
+        <v>0.1311</v>
       </c>
       <c r="D10" t="n">
-        <v>0.075</v>
+        <v>0.0898</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2999</v>
+        <v>1.2491</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9739</v>
+        <v>0.9661</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7351</v>
+        <v>1.615</v>
       </c>
     </row>
     <row r="11">
@@ -1195,22 +1194,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.098</v>
+        <v>-0.1671</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1677</v>
+        <v>0.1697</v>
       </c>
       <c r="D11" t="n">
-        <v>0.559</v>
+        <v>0.3249</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9066</v>
+        <v>0.8462</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6527</v>
+        <v>0.6067</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2595</v>
+        <v>1.1801</v>
       </c>
     </row>
     <row r="12">
@@ -1218,22 +1217,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.2421</v>
+        <v>-0.2554</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2499</v>
+        <v>0.2511</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3326</v>
+        <v>0.309</v>
       </c>
       <c r="E12" t="n">
-        <v>0.785</v>
+        <v>0.7746</v>
       </c>
       <c r="F12" t="n">
-        <v>0.481</v>
+        <v>0.4735</v>
       </c>
       <c r="G12" t="n">
-        <v>1.281</v>
+        <v>1.2671</v>
       </c>
     </row>
     <row r="13">
@@ -1241,22 +1240,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4407</v>
+        <v>-0.4521</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3576</v>
+        <v>0.351</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2177</v>
+        <v>0.1977</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6436</v>
+        <v>0.6363</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3193</v>
+        <v>0.3198</v>
       </c>
       <c r="G13" t="n">
-        <v>1.297</v>
+        <v>1.2659</v>
       </c>
     </row>
     <row r="14">
@@ -1264,22 +1263,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.5253</v>
+        <v>-0.5013</v>
       </c>
       <c r="C14" t="n">
-        <v>0.378</v>
+        <v>0.3646</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1647</v>
+        <v>0.1691</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5914</v>
+        <v>0.6057</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2819</v>
+        <v>0.2965</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2407</v>
+        <v>1.2376</v>
       </c>
     </row>
     <row r="15">
@@ -1287,22 +1286,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.5852</v>
+        <v>-0.5625</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3738</v>
+        <v>0.3604</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1174</v>
+        <v>0.1186</v>
       </c>
       <c r="E15" t="n">
-        <v>0.557</v>
+        <v>0.5698</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2677</v>
+        <v>0.2811</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1588</v>
+        <v>1.1549</v>
       </c>
     </row>
     <row r="16">
@@ -1310,22 +1309,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.5458</v>
+        <v>-0.5838</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3616</v>
+        <v>0.3499</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1312</v>
+        <v>0.0952</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5794</v>
+        <v>0.5578</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2852</v>
+        <v>0.281</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1769</v>
+        <v>1.1073</v>
       </c>
     </row>
     <row r="17">
@@ -1333,22 +1332,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4765</v>
+        <v>-0.5935</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3477</v>
+        <v>0.3387</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1705</v>
+        <v>0.0797</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6209</v>
+        <v>0.5524</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3141</v>
+        <v>0.2844</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2274</v>
+        <v>1.0729</v>
       </c>
     </row>
     <row r="18">
@@ -1356,22 +1355,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4667</v>
+        <v>-0.5683</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3396</v>
+        <v>0.3297</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1693</v>
+        <v>0.0848</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6271</v>
+        <v>0.5665</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3223</v>
+        <v>0.2969</v>
       </c>
       <c r="G18" t="n">
-        <v>1.22</v>
+        <v>1.0811</v>
       </c>
     </row>
     <row r="19">
@@ -1379,22 +1378,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.5035</v>
+        <v>-0.4958</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3396</v>
+        <v>0.3285</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1382</v>
+        <v>0.1312</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6044</v>
+        <v>0.6091</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3106</v>
+        <v>0.3199</v>
       </c>
       <c r="G19" t="n">
-        <v>1.176</v>
+        <v>1.1595</v>
       </c>
     </row>
     <row r="20">
@@ -1402,22 +1401,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.4435</v>
+        <v>-0.3746</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3478</v>
+        <v>0.3382</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2022</v>
+        <v>0.2681</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6418</v>
+        <v>0.6876</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3246</v>
+        <v>0.3543</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2688</v>
+        <v>1.3342</v>
       </c>
     </row>
     <row r="21">
@@ -1425,22 +1424,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.3859</v>
+        <v>-0.3389</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3503</v>
+        <v>0.3413</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2705</v>
+        <v>0.3208</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6798</v>
+        <v>0.7126</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3422</v>
+        <v>0.365</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3506</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="22">
@@ -1448,22 +1447,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.5485</v>
+        <v>-0.5358</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3539</v>
+        <v>0.3434</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1212</v>
+        <v>0.1187</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5778</v>
+        <v>0.5852</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2888</v>
+        <v>0.2985</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1563</v>
+        <v>1.1472</v>
       </c>
     </row>
     <row r="23">
@@ -1471,22 +1470,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.7638</v>
+        <v>-0.7809</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4418</v>
+        <v>0.4356</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0838</v>
+        <v>0.0731</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4659</v>
+        <v>0.458</v>
       </c>
       <c r="F23" t="n">
-        <v>0.196</v>
+        <v>0.195</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1075</v>
+        <v>1.0757</v>
       </c>
     </row>
     <row r="24">
@@ -1494,22 +1493,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.6584</v>
+        <v>-0.8011</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0589</v>
+        <v>0.0744</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5177</v>
+        <v>0.4488</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4613</v>
+        <v>0.388</v>
       </c>
       <c r="G24" t="n">
-        <v>0.581</v>
+        <v>0.5192</v>
       </c>
     </row>
   </sheetData>
@@ -1551,22 +1550,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6536</v>
+        <v>0.6463</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1937</v>
+        <v>1.1944</v>
       </c>
       <c r="D2" t="n">
-        <v>0.584</v>
+        <v>0.5884</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9225</v>
+        <v>1.9085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1853</v>
+        <v>0.1837</v>
       </c>
       <c r="G2" t="n">
-        <v>19.9503</v>
+        <v>19.8341</v>
       </c>
     </row>
     <row r="3">
@@ -1574,22 +1573,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2104</v>
+        <v>-0.2099</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28</v>
+        <v>0.2806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4523</v>
+        <v>0.4545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8103</v>
+        <v>0.8107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4681</v>
+        <v>0.4677</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4025</v>
+        <v>1.4051</v>
       </c>
     </row>
     <row r="4">
@@ -1600,19 +1599,19 @@
         <v>-0.1423</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2809</v>
+        <v>0.2822</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6125</v>
+        <v>0.6141</v>
       </c>
       <c r="E4" t="n">
         <v>0.8674</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5001</v>
+        <v>0.4989</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5043</v>
+        <v>1.5081</v>
       </c>
     </row>
     <row r="5">
@@ -1620,22 +1619,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7964</v>
+        <v>0.7981</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4608</v>
+        <v>0.4616</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0839</v>
+        <v>0.0838</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2176</v>
+        <v>2.2214</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8987</v>
+        <v>0.8989</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4718</v>
+        <v>5.4893</v>
       </c>
     </row>
     <row r="6">
@@ -1643,16 +1642,16 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-4.1308</v>
+        <v>-4.0057</v>
       </c>
       <c r="C6" t="n">
-        <v>31132.3064</v>
+        <v>27870.3231</v>
       </c>
       <c r="D6" t="n">
         <v>0.9999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0161</v>
+        <v>0.0182</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1666,22 +1665,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.1033</v>
+        <v>-0.104</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5976</v>
+        <v>0.5987</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8627</v>
+        <v>0.8622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9018</v>
+        <v>0.9013</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2795</v>
+        <v>0.2788</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9096</v>
+        <v>2.9138</v>
       </c>
     </row>
     <row r="8">
@@ -1689,16 +1688,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-4.2098</v>
+        <v>-4.1261</v>
       </c>
       <c r="C8" t="n">
-        <v>33127.983</v>
+        <v>52488.463</v>
       </c>
       <c r="D8" t="n">
         <v>0.9999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0148</v>
+        <v>0.0161</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1712,16 +1711,16 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-3.3352</v>
+        <v>-3.2341</v>
       </c>
       <c r="C9" t="n">
-        <v>34711.4847</v>
+        <v>20548.1592</v>
       </c>
       <c r="D9" t="n">
         <v>0.9999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0356</v>
+        <v>0.0394</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1735,22 +1734,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3199</v>
+        <v>0.3218</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4924</v>
+        <v>0.493</v>
       </c>
       <c r="D10" t="n">
-        <v>0.516</v>
+        <v>0.514</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3769</v>
+        <v>1.3796</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5245</v>
+        <v>0.5249</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6145</v>
+        <v>3.6259</v>
       </c>
     </row>
     <row r="11">
@@ -1758,22 +1757,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.3848</v>
+        <v>-0.2946</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6546</v>
+        <v>0.676</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5567</v>
+        <v>0.6629</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6806</v>
+        <v>0.7448</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1887</v>
+        <v>0.198</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4553</v>
+        <v>2.8019</v>
       </c>
     </row>
     <row r="12">
@@ -1781,22 +1780,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.1796</v>
+        <v>-0.1783</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8383</v>
+        <v>0.8375</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8304</v>
+        <v>0.8314</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8356</v>
+        <v>0.8367</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1616</v>
+        <v>0.1621</v>
       </c>
       <c r="G12" t="n">
-        <v>4.3206</v>
+        <v>4.3195</v>
       </c>
     </row>
     <row r="13">
@@ -1804,22 +1803,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.3215</v>
+        <v>-0.3191</v>
       </c>
       <c r="C13" t="n">
-        <v>1.2172</v>
+        <v>1.2167</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7917</v>
+        <v>0.7931</v>
       </c>
       <c r="E13" t="n">
-        <v>0.725</v>
+        <v>0.7268</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0667</v>
+        <v>0.067</v>
       </c>
       <c r="G13" t="n">
-        <v>7.8782</v>
+        <v>7.8902</v>
       </c>
     </row>
     <row r="14">
@@ -1827,22 +1826,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2983</v>
+        <v>-0.2951</v>
       </c>
       <c r="C14" t="n">
-        <v>1.2949</v>
+        <v>1.295</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8178</v>
+        <v>0.8198</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7421</v>
+        <v>0.7445</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0586</v>
+        <v>0.0588</v>
       </c>
       <c r="G14" t="n">
-        <v>9.3895</v>
+        <v>9.4229</v>
       </c>
     </row>
     <row r="15">
@@ -1850,22 +1849,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0764</v>
+        <v>-0.0727</v>
       </c>
       <c r="C15" t="n">
-        <v>1.2655</v>
+        <v>1.2659</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9519</v>
+        <v>0.9542</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9264</v>
+        <v>0.9299</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0776</v>
+        <v>0.0778</v>
       </c>
       <c r="G15" t="n">
-        <v>11.0659</v>
+        <v>11.116</v>
       </c>
     </row>
     <row r="16">
@@ -1873,22 +1872,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2627</v>
+        <v>0.266</v>
       </c>
       <c r="C16" t="n">
-        <v>1.183</v>
+        <v>1.1835</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8242</v>
+        <v>0.8222</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3005</v>
+        <v>1.3047</v>
       </c>
       <c r="F16" t="n">
-        <v>0.128</v>
+        <v>0.1283</v>
       </c>
       <c r="G16" t="n">
-        <v>13.2141</v>
+        <v>13.2708</v>
       </c>
     </row>
     <row r="17">
@@ -1896,22 +1895,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6006</v>
+        <v>0.6012</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1302</v>
+        <v>1.1306</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5952</v>
+        <v>0.5949</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8232</v>
+        <v>1.8243</v>
       </c>
       <c r="F17" t="n">
-        <v>0.199</v>
+        <v>0.1989</v>
       </c>
       <c r="G17" t="n">
-        <v>16.7071</v>
+        <v>16.7281</v>
       </c>
     </row>
     <row r="18">
@@ -1919,22 +1918,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1185</v>
+        <v>1.1187</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4761</v>
+        <v>0.4773</v>
       </c>
       <c r="E18" t="n">
-        <v>2.219</v>
+        <v>2.2144</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2478</v>
+        <v>0.2472</v>
       </c>
       <c r="G18" t="n">
-        <v>19.8728</v>
+        <v>19.837</v>
       </c>
     </row>
     <row r="19">
@@ -1942,22 +1941,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3992</v>
+        <v>0.4054</v>
       </c>
       <c r="C19" t="n">
-        <v>1.119</v>
+        <v>1.1192</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7213</v>
+        <v>0.7172</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4906</v>
+        <v>1.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1663</v>
+        <v>0.1673</v>
       </c>
       <c r="G19" t="n">
-        <v>13.3622</v>
+        <v>13.4508</v>
       </c>
     </row>
     <row r="20">
@@ -1965,22 +1964,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0343</v>
+        <v>0.043</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1592</v>
+        <v>1.1589</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9764</v>
+        <v>0.9704</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0348</v>
+        <v>1.0439</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1067</v>
+        <v>0.1077</v>
       </c>
       <c r="G20" t="n">
-        <v>10.0359</v>
+        <v>10.119</v>
       </c>
     </row>
     <row r="21">
@@ -1988,22 +1987,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0067</v>
+        <v>0.0119</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1774</v>
+        <v>1.1769</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9955</v>
+        <v>0.9919</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0067</v>
+        <v>1.012</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1002</v>
+        <v>0.1008</v>
       </c>
       <c r="G21" t="n">
-        <v>10.1188</v>
+        <v>10.1612</v>
       </c>
     </row>
     <row r="22">
@@ -2011,22 +2010,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2032</v>
+        <v>0.2049</v>
       </c>
       <c r="C22" t="n">
-        <v>1.1655</v>
+        <v>1.1658</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8616</v>
+        <v>0.8605</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2253</v>
+        <v>1.2274</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1248</v>
+        <v>0.1249</v>
       </c>
       <c r="G22" t="n">
-        <v>12.0323</v>
+        <v>12.0586</v>
       </c>
     </row>
     <row r="23">
@@ -2034,22 +2033,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>0.4415</v>
+        <v>0.4398</v>
       </c>
       <c r="C23" t="n">
-        <v>1.4466</v>
+        <v>1.4464</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7602</v>
+        <v>0.7611</v>
       </c>
       <c r="E23" t="n">
-        <v>1.555</v>
+        <v>1.5524</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0913</v>
+        <v>0.0912</v>
       </c>
       <c r="G23" t="n">
-        <v>26.4917</v>
+        <v>26.4345</v>
       </c>
     </row>
     <row r="24">
@@ -2057,22 +2056,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.2729</v>
+        <v>-0.2693</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1272</v>
+        <v>0.1276</v>
       </c>
       <c r="D24" t="n">
-        <v>0.032</v>
+        <v>0.0348</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7612</v>
+        <v>0.7639</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5932</v>
+        <v>0.5948</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9768</v>
+        <v>0.981</v>
       </c>
     </row>
   </sheetData>
@@ -2114,22 +2113,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>2.8062</v>
+        <v>2.8515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1794</v>
+        <v>0.1561</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>16.5472</v>
+        <v>17.3144</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6429</v>
+        <v>12.75</v>
       </c>
       <c r="G2" t="n">
-        <v>23.5174</v>
+        <v>23.5128</v>
       </c>
     </row>
     <row r="3">
@@ -2137,22 +2136,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0303</v>
+        <v>0.0567</v>
       </c>
       <c r="C3" t="n">
-        <v>0.049</v>
+        <v>0.0461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5363</v>
+        <v>0.2185</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0307</v>
+        <v>1.0583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9364</v>
+        <v>0.967</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1346</v>
+        <v>1.1583</v>
       </c>
     </row>
     <row r="4">
@@ -2160,22 +2159,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0409</v>
+        <v>0.0692</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0459</v>
+        <v>0.0433</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3729</v>
+        <v>0.1103</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0417</v>
+        <v>1.0716</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9521</v>
+        <v>0.9844</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1398</v>
+        <v>1.1666</v>
       </c>
     </row>
     <row r="5">
@@ -2183,22 +2182,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0062</v>
+        <v>0.0263</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0808</v>
+        <v>0.0673</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9385</v>
+        <v>0.6959</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0063</v>
+        <v>1.0267</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8588</v>
+        <v>0.8998</v>
       </c>
       <c r="G5" t="n">
-        <v>1.179</v>
+        <v>1.1715</v>
       </c>
     </row>
     <row r="6">
@@ -2206,22 +2205,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0508</v>
+        <v>-0.5507</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09</v>
+        <v>4.5132</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5723</v>
+        <v>0.9029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9504</v>
+        <v>0.5765</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7967</v>
+        <v>0.0001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1339</v>
+        <v>4003.7986</v>
       </c>
     </row>
     <row r="7">
@@ -2229,68 +2228,58 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0425</v>
+        <v>0.0249</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0822</v>
+        <v>0.0684</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6055</v>
+        <v>0.7165</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0434</v>
+        <v>1.0252</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8881</v>
+        <v>0.8965</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2259</v>
+        <v>1.1723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="n">
-        <v>-0.0705</v>
-      </c>
+      <c r="B8"/>
       <c r="C8" t="n">
-        <v>0.0929</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9319</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.7768</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.1181</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1751</v>
+        <v>-0.1888</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1048</v>
+        <v>0.0912</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0948</v>
+        <v>0.0384</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8394</v>
+        <v>0.828</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6835</v>
+        <v>0.6925</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0308</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -2298,22 +2287,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.1305</v>
+        <v>-0.1155</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0857</v>
+        <v>0.0691</v>
       </c>
       <c r="D10" t="n">
-        <v>0.128</v>
+        <v>0.0945</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8777</v>
+        <v>0.8909</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7419</v>
+        <v>0.7781</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0383</v>
+        <v>1.0201</v>
       </c>
     </row>
     <row r="11">
@@ -2321,22 +2310,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.1154</v>
+        <v>-0.0729</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0932</v>
+        <v>0.0859</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2155</v>
+        <v>0.3956</v>
       </c>
       <c r="E11" t="n">
-        <v>0.891</v>
+        <v>0.9297</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7423</v>
+        <v>0.7857</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0695</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -2344,22 +2333,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0717</v>
+        <v>-0.0856</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1281</v>
+        <v>0.1165</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5758</v>
+        <v>0.4626</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9308</v>
+        <v>0.918</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7241</v>
+        <v>0.7305</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1965</v>
+        <v>1.1535</v>
       </c>
     </row>
     <row r="13">
@@ -2367,22 +2356,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.1335</v>
+        <v>-0.1562</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1793</v>
+        <v>0.1595</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4565</v>
+        <v>0.3275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.875</v>
+        <v>0.8554</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6158</v>
+        <v>0.6258</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2434</v>
+        <v>1.1693</v>
       </c>
     </row>
     <row r="14">
@@ -2390,22 +2379,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.15</v>
+        <v>-0.1551</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1866</v>
+        <v>0.1628</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4216</v>
+        <v>0.3407</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8607</v>
+        <v>0.8563</v>
       </c>
       <c r="F14" t="n">
-        <v>0.597</v>
+        <v>0.6223</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2408</v>
+        <v>1.1782</v>
       </c>
     </row>
     <row r="15">
@@ -2413,22 +2402,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.1739</v>
+        <v>-0.1573</v>
       </c>
       <c r="C15" t="n">
-        <v>0.183</v>
+        <v>0.1594</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3419</v>
+        <v>0.3236</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8404</v>
+        <v>0.8544</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5871</v>
+        <v>0.6252</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2029</v>
+        <v>1.1677</v>
       </c>
     </row>
     <row r="16">
@@ -2436,22 +2425,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.2197</v>
+        <v>-0.2084</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1755</v>
+        <v>0.1531</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2106</v>
+        <v>0.1734</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8027</v>
+        <v>0.8119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5691</v>
+        <v>0.6014</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1323</v>
+        <v>1.096</v>
       </c>
     </row>
     <row r="17">
@@ -2459,22 +2448,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.2461</v>
+        <v>-0.2581</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1704</v>
+        <v>0.1501</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1487</v>
+        <v>0.0856</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7818</v>
+        <v>0.7725</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5598</v>
+        <v>0.5756</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0919</v>
+        <v>1.0368</v>
       </c>
     </row>
     <row r="18">
@@ -2482,22 +2471,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.2325</v>
+        <v>-0.2702</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1667</v>
+        <v>0.1473</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1632</v>
+        <v>0.0666</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7925</v>
+        <v>0.7632</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5716</v>
+        <v>0.5718</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0989</v>
+        <v>1.0187</v>
       </c>
     </row>
     <row r="19">
@@ -2505,22 +2494,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.1979</v>
+        <v>-0.2424</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1663</v>
+        <v>0.1462</v>
       </c>
       <c r="D19" t="n">
-        <v>0.234</v>
+        <v>0.0974</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8205</v>
+        <v>0.7847</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5923</v>
+        <v>0.5892</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1365</v>
+        <v>1.0452</v>
       </c>
     </row>
     <row r="20">
@@ -2528,22 +2517,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.1916</v>
+        <v>-0.2176</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1729</v>
+        <v>0.153</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2678</v>
+        <v>0.155</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8256</v>
+        <v>0.8045</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5883</v>
+        <v>0.596</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1587</v>
+        <v>1.0858</v>
       </c>
     </row>
     <row r="21">
@@ -2551,22 +2540,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.2</v>
+        <v>-0.2047</v>
       </c>
       <c r="C21" t="n">
-        <v>0.177</v>
+        <v>0.1568</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2585</v>
+        <v>0.1917</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8187</v>
+        <v>0.8149</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5787</v>
+        <v>0.5992</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1583</v>
+        <v>1.1081</v>
       </c>
     </row>
     <row r="22">
@@ -2574,22 +2563,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.1708</v>
+        <v>-0.157</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1814</v>
+        <v>0.1587</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3462</v>
+        <v>0.3224</v>
       </c>
       <c r="E22" t="n">
-        <v>0.843</v>
+        <v>0.8547</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5908</v>
+        <v>0.6262</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2028</v>
+        <v>1.1665</v>
       </c>
     </row>
     <row r="23">
@@ -2597,22 +2586,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.1306</v>
+        <v>-0.0983</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2335</v>
+        <v>0.2061</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5759</v>
+        <v>0.6335</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8775</v>
+        <v>0.9064</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5552</v>
+        <v>0.6052</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3869</v>
+        <v>1.3575</v>
       </c>
     </row>
     <row r="24">
@@ -2620,22 +2609,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.5118</v>
+        <v>-1.7845</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0797</v>
+        <v>0.0918</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2205</v>
+        <v>0.1679</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1886</v>
+        <v>0.1402</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2578</v>
+        <v>0.201</v>
       </c>
     </row>
   </sheetData>
@@ -2677,22 +2666,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>3.6956</v>
+        <v>3.6802</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5517</v>
+        <v>0.6289</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>40.2687</v>
+        <v>39.6531</v>
       </c>
       <c r="F2" t="n">
-        <v>13.6576</v>
+        <v>11.5602</v>
       </c>
       <c r="G2" t="n">
-        <v>118.7305</v>
+        <v>136.0155</v>
       </c>
     </row>
     <row r="3">
@@ -2700,22 +2689,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0617</v>
+        <v>0.0839</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0931</v>
+        <v>0.0983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5074</v>
+        <v>0.3934</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0637</v>
+        <v>1.0875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8862</v>
+        <v>0.8969</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2766</v>
+        <v>1.3187</v>
       </c>
     </row>
     <row r="4">
@@ -2723,22 +2712,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0038</v>
+        <v>0.0332</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0992</v>
+        <v>0.106</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9695</v>
+        <v>0.7541</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9962</v>
+        <v>1.0337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8201</v>
+        <v>0.8399</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2101</v>
+        <v>1.2724</v>
       </c>
     </row>
     <row r="5">
@@ -2746,22 +2735,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5066</v>
+        <v>0.5702</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4029</v>
+        <v>0.4853</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2086</v>
+        <v>0.24</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6597</v>
+        <v>1.7686</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7535</v>
+        <v>0.6832</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6557</v>
+        <v>4.5786</v>
       </c>
     </row>
     <row r="6">
@@ -2769,22 +2758,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2732</v>
+        <v>0.4384</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4071</v>
+        <v>0.4909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5022</v>
+        <v>0.3718</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3141</v>
+        <v>1.5502</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5917</v>
+        <v>0.5923</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9184</v>
+        <v>4.0575</v>
       </c>
     </row>
     <row r="7">
@@ -2792,22 +2781,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3417</v>
+        <v>0.3963</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4097</v>
+        <v>0.4898</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4043</v>
+        <v>0.4184</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4074</v>
+        <v>1.4863</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6305</v>
+        <v>0.5691</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1416</v>
+        <v>3.8814</v>
       </c>
     </row>
     <row r="8">
@@ -2815,22 +2804,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0368</v>
+        <v>0.1349</v>
       </c>
       <c r="C8" t="n">
-        <v>0.508</v>
+        <v>0.6714</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9422</v>
+        <v>0.8408</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9639</v>
+        <v>1.1444</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3561</v>
+        <v>0.307</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6086</v>
+        <v>4.2665</v>
       </c>
     </row>
     <row r="9">
@@ -2838,22 +2827,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0543</v>
+        <v>0.1153</v>
       </c>
       <c r="C9" t="n">
-        <v>0.467</v>
+        <v>0.5378</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9074</v>
+        <v>0.8302</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0558</v>
+        <v>1.1222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4228</v>
+        <v>0.3911</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6367</v>
+        <v>3.2199</v>
       </c>
     </row>
     <row r="10">
@@ -2861,22 +2850,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0394</v>
+        <v>0.0726</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4375</v>
+        <v>0.4947</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9282</v>
+        <v>0.8833</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0402</v>
+        <v>1.0753</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4413</v>
+        <v>0.4078</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4519</v>
+        <v>2.8355</v>
       </c>
     </row>
     <row r="11">
@@ -2884,22 +2873,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2517</v>
+        <v>0.0556</v>
       </c>
       <c r="C11" t="n">
-        <v>0.407</v>
+        <v>0.5695</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5363</v>
+        <v>0.9222</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2862</v>
+        <v>1.0572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5792</v>
+        <v>0.3463</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8563</v>
+        <v>3.2277</v>
       </c>
     </row>
     <row r="12">
@@ -2907,22 +2896,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.3645</v>
+        <v>-0.408</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3331</v>
+        <v>0.3662</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2739</v>
+        <v>0.2652</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6946</v>
+        <v>0.665</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3615</v>
+        <v>0.3244</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3344</v>
+        <v>1.363</v>
       </c>
     </row>
     <row r="13">
@@ -2930,22 +2919,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.6841</v>
+        <v>-0.7641</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4614</v>
+        <v>0.5001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1382</v>
+        <v>0.1265</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5046</v>
+        <v>0.4657</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2043</v>
+        <v>0.1748</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2464</v>
+        <v>1.2412</v>
       </c>
     </row>
     <row r="14">
@@ -2953,22 +2942,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.7966</v>
+        <v>-0.8866</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4828</v>
+        <v>0.5214</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0989</v>
+        <v>0.0891</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4509</v>
+        <v>0.412</v>
       </c>
       <c r="F14" t="n">
-        <v>0.175</v>
+        <v>0.1483</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1614</v>
+        <v>1.145</v>
       </c>
     </row>
     <row r="15">
@@ -2976,22 +2965,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.7271</v>
+        <v>-0.8038</v>
       </c>
       <c r="C15" t="n">
-        <v>0.461</v>
+        <v>0.497</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1147</v>
+        <v>0.1058</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4833</v>
+        <v>0.4476</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1958</v>
+        <v>0.169</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1929</v>
+        <v>1.1857</v>
       </c>
     </row>
     <row r="16">
@@ -2999,22 +2988,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.5878</v>
+        <v>-0.6345</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4163</v>
+        <v>0.4444</v>
       </c>
       <c r="D16" t="n">
-        <v>0.158</v>
+        <v>0.1534</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5555</v>
+        <v>0.5302</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2457</v>
+        <v>0.2219</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2563</v>
+        <v>1.2669</v>
       </c>
     </row>
     <row r="17">
@@ -3022,22 +3011,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.4762</v>
+        <v>-0.4972</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3919</v>
+        <v>0.4199</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2243</v>
+        <v>0.2364</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6211</v>
+        <v>0.6082</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2881</v>
+        <v>0.2671</v>
       </c>
       <c r="G17" t="n">
-        <v>1.339</v>
+        <v>1.3852</v>
       </c>
     </row>
     <row r="18">
@@ -3045,22 +3034,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.4278</v>
+        <v>-0.4639</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3856</v>
+        <v>0.4149</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2673</v>
+        <v>0.2636</v>
       </c>
       <c r="E18" t="n">
-        <v>0.652</v>
+        <v>0.6289</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3062</v>
+        <v>0.2789</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3883</v>
+        <v>1.4181</v>
       </c>
     </row>
     <row r="19">
@@ -3068,22 +3057,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.4209</v>
+        <v>-0.5068</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3858</v>
+        <v>0.4152</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2753</v>
+        <v>0.2222</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6564</v>
+        <v>0.6024</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3082</v>
+        <v>0.267</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3983</v>
+        <v>1.3592</v>
       </c>
     </row>
     <row r="20">
@@ -3091,22 +3080,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.4618</v>
+        <v>-0.5096</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4089</v>
+        <v>0.4476</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2587</v>
+        <v>0.255</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6301</v>
+        <v>0.6008</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2827</v>
+        <v>0.2498</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4044</v>
+        <v>1.4445</v>
       </c>
     </row>
     <row r="21">
@@ -3114,22 +3103,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.5497</v>
+        <v>-0.5398</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4485</v>
+        <v>0.5075</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2203</v>
+        <v>0.2875</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5771</v>
+        <v>0.5829</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2396</v>
+        <v>0.2156</v>
       </c>
       <c r="G21" t="n">
-        <v>1.39</v>
+        <v>1.576</v>
       </c>
     </row>
     <row r="22">
@@ -3137,22 +3126,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.6302</v>
+        <v>-0.581</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5566</v>
+        <v>0.6195</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2575</v>
+        <v>0.3483</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5325</v>
+        <v>0.5593</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1789</v>
+        <v>0.1661</v>
       </c>
       <c r="G22" t="n">
-        <v>1.5852</v>
+        <v>1.8836</v>
       </c>
     </row>
     <row r="23">
@@ -3160,22 +3149,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.7091</v>
+        <v>-0.6241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8097</v>
+        <v>0.8835</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3812</v>
+        <v>0.48</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4921</v>
+        <v>0.5357</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1006</v>
+        <v>0.0948</v>
       </c>
       <c r="G23" t="n">
-        <v>2.406</v>
+        <v>3.0271</v>
       </c>
     </row>
     <row r="24">
@@ -3183,22 +3172,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.2996</v>
+        <v>-1.3133</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1361</v>
+        <v>0.1402</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2726</v>
+        <v>0.2689</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2088</v>
+        <v>0.2043</v>
       </c>
       <c r="G24" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
     </row>
   </sheetData>
@@ -3240,22 +3229,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>2.315</v>
+        <v>2.317</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2838</v>
+        <v>0.2861</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1249</v>
+        <v>10.1453</v>
       </c>
       <c r="F2" t="n">
-        <v>5.8048</v>
+        <v>5.7903</v>
       </c>
       <c r="G2" t="n">
-        <v>17.66</v>
+        <v>17.7759</v>
       </c>
     </row>
     <row r="3">
@@ -3263,22 +3252,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2653</v>
+        <v>-0.2679</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0817</v>
+        <v>0.0823</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0012</v>
+        <v>0.0011</v>
       </c>
       <c r="E3" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6535</v>
+        <v>0.651</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9002</v>
+        <v>0.8989</v>
       </c>
     </row>
     <row r="4">
@@ -3286,22 +3275,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.3223</v>
+        <v>-0.3253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0884</v>
+        <v>0.0892</v>
       </c>
       <c r="D4" t="n">
         <v>0.0003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7245</v>
+        <v>0.7223</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6092</v>
+        <v>0.6064</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8615</v>
+        <v>0.8603</v>
       </c>
     </row>
     <row r="5">
@@ -3309,22 +3298,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2152</v>
+        <v>0.2128</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1585</v>
+        <v>0.1591</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1745</v>
+        <v>0.1811</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2401</v>
+        <v>1.2372</v>
       </c>
       <c r="F5" t="n">
-        <v>0.909</v>
+        <v>0.9057</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6919</v>
+        <v>1.6899</v>
       </c>
     </row>
     <row r="6">
@@ -3332,22 +3321,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.3065</v>
+        <v>-0.2567</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2529</v>
+        <v>0.2879</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2254</v>
+        <v>0.3726</v>
       </c>
       <c r="E6" t="n">
-        <v>0.736</v>
+        <v>0.7736</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4484</v>
+        <v>0.4399</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2081</v>
+        <v>1.3602</v>
       </c>
     </row>
     <row r="7">
@@ -3355,22 +3344,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2063</v>
+        <v>0.2058</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1625</v>
+        <v>0.1629</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2041</v>
+        <v>0.2066</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2292</v>
+        <v>1.2285</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8939</v>
+        <v>0.8927</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6901</v>
+        <v>1.6906</v>
       </c>
     </row>
     <row r="8">
@@ -3378,22 +3367,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4051</v>
+        <v>-0.2945</v>
       </c>
       <c r="C8" t="n">
-        <v>0.342</v>
+        <v>0.4668</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2362</v>
+        <v>0.5281</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6669</v>
+        <v>0.7449</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3412</v>
+        <v>0.2983</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3037</v>
+        <v>1.8598</v>
       </c>
     </row>
     <row r="9">
@@ -3401,22 +3390,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3051</v>
+        <v>0.3042</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1764</v>
+        <v>0.1769</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0836</v>
+        <v>0.0856</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3568</v>
+        <v>1.3555</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9602</v>
+        <v>0.9583</v>
       </c>
       <c r="G9" t="n">
-        <v>1.917</v>
+        <v>1.9174</v>
       </c>
     </row>
     <row r="10">
@@ -3427,19 +3416,19 @@
         <v>0.061</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1622</v>
+        <v>0.1625</v>
       </c>
       <c r="D10" t="n">
-        <v>0.707</v>
+        <v>0.7073</v>
       </c>
       <c r="E10" t="n">
         <v>1.0629</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7734</v>
+        <v>0.773</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4607</v>
+        <v>1.4617</v>
       </c>
     </row>
     <row r="11">
@@ -3447,22 +3436,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.4734</v>
+        <v>-0.4552</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5145</v>
+        <v>0.5545</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3575</v>
+        <v>0.4117</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6229</v>
+        <v>0.6343</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2272</v>
+        <v>0.214</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7073</v>
+        <v>1.8805</v>
       </c>
     </row>
     <row r="12">
@@ -3470,22 +3459,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0528</v>
+        <v>-0.0536</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1969</v>
+        <v>0.1995</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7886</v>
+        <v>0.7882</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9486</v>
+        <v>0.9478</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6449</v>
+        <v>0.6411</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3952</v>
+        <v>1.4014</v>
       </c>
     </row>
     <row r="13">
@@ -3493,22 +3482,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0986</v>
+        <v>-0.1002</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2659</v>
+        <v>0.2689</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7109</v>
+        <v>0.7095</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9061</v>
+        <v>0.9047</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5381</v>
+        <v>0.5341</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5258</v>
+        <v>1.5323</v>
       </c>
     </row>
     <row r="14">
@@ -3516,22 +3505,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.1032</v>
+        <v>-0.1058</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2718</v>
+        <v>0.2745</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7043</v>
+        <v>0.6999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.902</v>
+        <v>0.8996</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5295</v>
+        <v>0.5253</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5365</v>
+        <v>1.5407</v>
       </c>
     </row>
     <row r="15">
@@ -3539,22 +3528,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0517</v>
+        <v>-0.0546</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2678</v>
+        <v>0.2706</v>
       </c>
       <c r="D15" t="n">
-        <v>0.847</v>
+        <v>0.84</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9497</v>
+        <v>0.9469</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5618</v>
+        <v>0.5572</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6051</v>
+        <v>1.6091</v>
       </c>
     </row>
     <row r="16">
@@ -3562,22 +3551,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0129</v>
+        <v>0.0117</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2559</v>
+        <v>0.2584</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9599</v>
+        <v>0.9639</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0129</v>
+        <v>1.0118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6134</v>
+        <v>0.6097</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6726</v>
+        <v>1.6789</v>
       </c>
     </row>
     <row r="17">
@@ -3585,22 +3574,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0513</v>
+        <v>0.0536</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2506</v>
+        <v>0.2533</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8379</v>
+        <v>0.8325</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0526</v>
+        <v>1.055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6441</v>
+        <v>0.6422</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7203</v>
+        <v>1.7332</v>
       </c>
     </row>
     <row r="18">
@@ -3608,22 +3597,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0151</v>
+        <v>0.0173</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2487</v>
+        <v>0.2513</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9516</v>
+        <v>0.9451</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0152</v>
+        <v>1.0174</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6236</v>
+        <v>0.6217</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6528</v>
+        <v>1.6651</v>
       </c>
     </row>
     <row r="19">
@@ -3631,22 +3620,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.0803</v>
+        <v>-0.083</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2484</v>
+        <v>0.251</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7466</v>
+        <v>0.7409</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9229</v>
+        <v>0.9204</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5671</v>
+        <v>0.5628</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5018</v>
+        <v>1.5052</v>
       </c>
     </row>
     <row r="20">
@@ -3654,22 +3643,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.1165</v>
+        <v>-0.1227</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2637</v>
+        <v>0.2667</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6586</v>
+        <v>0.6456</v>
       </c>
       <c r="E20" t="n">
-        <v>0.89</v>
+        <v>0.8845</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5308</v>
+        <v>0.5244</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4923</v>
+        <v>1.492</v>
       </c>
     </row>
     <row r="21">
@@ -3677,22 +3666,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0855</v>
+        <v>-0.0913</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2735</v>
+        <v>0.2768</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7547</v>
+        <v>0.7414</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9181</v>
+        <v>0.9127</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5371</v>
+        <v>0.5305</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5693</v>
+        <v>1.5702</v>
       </c>
     </row>
     <row r="22">
@@ -3700,22 +3689,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0216</v>
+        <v>-0.0236</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2851</v>
+        <v>0.288</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9396</v>
+        <v>0.9347</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9786</v>
+        <v>0.9767</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5596</v>
+        <v>0.5554</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7113</v>
+        <v>1.7174</v>
       </c>
     </row>
     <row r="23">
@@ -3723,22 +3712,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>0.048</v>
+        <v>0.0503</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3831</v>
+        <v>0.3873</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9003</v>
+        <v>0.8967</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0492</v>
+        <v>1.0516</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4951</v>
+        <v>0.4922</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2232</v>
+        <v>2.2468</v>
       </c>
     </row>
     <row r="24">
@@ -3746,22 +3735,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.3513</v>
+        <v>-1.3457</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0814</v>
+        <v>0.0823</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2589</v>
+        <v>0.2603</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2207</v>
+        <v>0.2216</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3037</v>
+        <v>0.3059</v>
       </c>
     </row>
   </sheetData>
@@ -3803,22 +3792,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>3.3025</v>
+        <v>3.2683</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2803</v>
+        <v>0.4537</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0099</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>27.1793</v>
+        <v>26.2657</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2101</v>
+        <v>10.7938</v>
       </c>
       <c r="G2" t="n">
-        <v>334.2463</v>
+        <v>63.9153</v>
       </c>
     </row>
     <row r="3">
@@ -3826,22 +3815,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5262</v>
+        <v>-0.1526</v>
       </c>
       <c r="C3" t="n">
-        <v>0.243</v>
+        <v>0.1426</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0303</v>
+        <v>0.2845</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6924</v>
+        <v>0.8584</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0513</v>
+        <v>0.6491</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7247</v>
+        <v>1.1353</v>
       </c>
     </row>
     <row r="4">
@@ -3849,22 +3838,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3542</v>
+        <v>0.1722</v>
       </c>
       <c r="C4" t="n">
-        <v>0.233</v>
+        <v>0.1217</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1285</v>
+        <v>0.1572</v>
       </c>
       <c r="E4" t="n">
-        <v>1.425</v>
+        <v>1.1879</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9025</v>
+        <v>0.9358</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2501</v>
+        <v>1.508</v>
       </c>
     </row>
     <row r="5">
@@ -3872,22 +3861,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1365</v>
+        <v>0.1378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6849</v>
+        <v>0.2059</v>
       </c>
       <c r="D5" t="n">
-        <v>0.842</v>
+        <v>0.5034</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1463</v>
+        <v>1.1477</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2994</v>
+        <v>0.7666</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3885</v>
+        <v>1.7183</v>
       </c>
     </row>
     <row r="6">
@@ -3895,22 +3884,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.607</v>
+        <v>-0.0833</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5845</v>
+        <v>0.2629</v>
       </c>
       <c r="D6" t="n">
-        <v>0.299</v>
+        <v>0.7513</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8349</v>
+        <v>0.9201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5836</v>
+        <v>0.5496</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7691</v>
+        <v>1.5402</v>
       </c>
     </row>
     <row r="7">
@@ -3918,22 +3907,22 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.2895</v>
+        <v>0.1858</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7234</v>
+        <v>0.2097</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6891</v>
+        <v>0.3756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7487</v>
+        <v>1.2041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1813</v>
+        <v>0.7984</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0907</v>
+        <v>1.8161</v>
       </c>
     </row>
     <row r="8">
@@ -3941,22 +3930,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6646</v>
+        <v>-0.2644</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5659</v>
+        <v>0.4337</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2402</v>
+        <v>0.5421</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9438</v>
+        <v>0.7676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6411</v>
+        <v>0.3281</v>
       </c>
       <c r="G8" t="n">
-        <v>5.8934</v>
+        <v>1.7961</v>
       </c>
     </row>
     <row r="9">
@@ -3964,22 +3953,22 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4127</v>
+        <v>-0.1258</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7752</v>
+        <v>0.2555</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5945</v>
+        <v>0.6224</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6618</v>
+        <v>0.8818</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1448</v>
+        <v>0.5344</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0243</v>
+        <v>1.4549</v>
       </c>
     </row>
     <row r="10">
@@ -3987,22 +3976,22 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.0377</v>
+        <v>-0.6746</v>
       </c>
       <c r="C10" t="n">
-        <v>2189.6613</v>
+        <v>0.2244</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9993</v>
+        <v>0.0026</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1303</v>
+        <v>0.5094</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="e">
-        <v>#NUM!</v>
+        <v>0.3281</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7907</v>
       </c>
     </row>
     <row r="11">
@@ -4010,22 +3999,22 @@
         <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>-1.4508</v>
+        <v>-0.009</v>
       </c>
       <c r="C11" t="n">
-        <v>2981.6323</v>
+        <v>0.2328</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9996</v>
+        <v>0.9691</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2344</v>
+        <v>0.991</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="e">
-        <v>#NUM!</v>
+        <v>0.628</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5639</v>
       </c>
     </row>
     <row r="12">
@@ -4033,22 +4022,22 @@
         <v>17</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.2623</v>
+        <v>-0.2076</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9743</v>
+        <v>0.3311</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1951</v>
+        <v>0.5307</v>
       </c>
       <c r="E12" t="n">
-        <v>0.283</v>
+        <v>0.8126</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0419</v>
+        <v>0.4247</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9104</v>
+        <v>1.5547</v>
       </c>
     </row>
     <row r="13">
@@ -4056,22 +4045,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.3668</v>
+        <v>-0.3644</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4649</v>
+        <v>0.4594</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1062</v>
+        <v>0.4276</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0938</v>
+        <v>0.6946</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0053</v>
+        <v>0.2823</v>
       </c>
       <c r="G13" t="n">
-        <v>1.656</v>
+        <v>1.709</v>
       </c>
     </row>
     <row r="14">
@@ -4079,22 +4068,22 @@
         <v>19</v>
       </c>
       <c r="B14" t="n">
-        <v>-2.9957</v>
+        <v>-0.3074</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7185</v>
+        <v>0.4752</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0813</v>
+        <v>0.5178</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05</v>
+        <v>0.7354</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0017</v>
+        <v>0.2897</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4513</v>
+        <v>1.8665</v>
       </c>
     </row>
     <row r="15">
@@ -4102,22 +4091,22 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-3.2126</v>
+        <v>-0.2631</v>
       </c>
       <c r="C15" t="n">
-        <v>1.744</v>
+        <v>0.4665</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0655</v>
+        <v>0.5728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0403</v>
+        <v>0.7686</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0013</v>
+        <v>0.308</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2282</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="16">
@@ -4125,22 +4114,22 @@
         <v>21</v>
       </c>
       <c r="B16" t="n">
-        <v>-3.1079</v>
+        <v>-0.3358</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5638</v>
+        <v>0.4459</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0469</v>
+        <v>0.4514</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0447</v>
+        <v>0.7148</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0021</v>
+        <v>0.2983</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9579</v>
+        <v>1.7128</v>
       </c>
     </row>
     <row r="17">
@@ -4148,22 +4137,22 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>-2.7713</v>
+        <v>-0.4363</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3013</v>
+        <v>0.4352</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0332</v>
+        <v>0.3161</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0626</v>
+        <v>0.6464</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0049</v>
+        <v>0.2755</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8019</v>
+        <v>1.5169</v>
       </c>
     </row>
     <row r="18">
@@ -4171,22 +4160,22 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>-2.2698</v>
+        <v>-0.5104</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1417</v>
+        <v>0.4285</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0468</v>
+        <v>0.2336</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1033</v>
+        <v>0.6002</v>
       </c>
       <c r="F18" t="n">
-        <v>0.011</v>
+        <v>0.2592</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9684</v>
+        <v>1.3902</v>
       </c>
     </row>
     <row r="19">
@@ -4194,22 +4183,22 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>-2.1592</v>
+        <v>-0.5017</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1317</v>
+        <v>0.4283</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0564</v>
+        <v>0.2414</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1154</v>
+        <v>0.6055</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0126</v>
+        <v>0.2615</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0606</v>
+        <v>1.4017</v>
       </c>
     </row>
     <row r="20">
@@ -4217,22 +4206,22 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>-2.2244</v>
+        <v>-0.4296</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1697</v>
+        <v>0.4484</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0572</v>
+        <v>0.338</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1081</v>
+        <v>0.6508</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0109</v>
+        <v>0.2702</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0705</v>
+        <v>1.5671</v>
       </c>
     </row>
     <row r="21">
@@ -4240,22 +4229,22 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>-2.0845</v>
+        <v>-0.2233</v>
       </c>
       <c r="C21" t="n">
-        <v>1.187</v>
+        <v>0.4608</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0791</v>
+        <v>0.628</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1244</v>
+        <v>0.7999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0121</v>
+        <v>0.3242</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2738</v>
+        <v>1.9736</v>
       </c>
     </row>
     <row r="22">
@@ -4263,22 +4252,22 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>-2.3118</v>
+        <v>0.0322</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2185</v>
+        <v>0.4778</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0578</v>
+        <v>0.9462</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0991</v>
+        <v>1.0328</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0091</v>
+        <v>0.4049</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0795</v>
+        <v>2.6344</v>
       </c>
     </row>
     <row r="23">
@@ -4286,22 +4275,22 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>-2.6108</v>
+        <v>0.2795</v>
       </c>
       <c r="C23" t="n">
-        <v>1.5281</v>
+        <v>0.6199</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0875</v>
+        <v>0.6521</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0735</v>
+        <v>1.3224</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0037</v>
+        <v>0.3924</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4684</v>
+        <v>4.4568</v>
       </c>
     </row>
     <row r="24">
@@ -4309,585 +4298,22 @@
         <v>29</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.9765</v>
+        <v>-0.4692</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2063</v>
+        <v>0.0851</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3766</v>
+        <v>0.6255</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2514</v>
+        <v>0.5294</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5643</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.5094</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>26.3105</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9.6939</v>
-      </c>
-      <c r="G2" t="n">
-        <v>71.41</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-0.0697</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.1491</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9326</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6963</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.2493</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.2093</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.1289</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1044</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.2329</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.5873</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.0263</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2367</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9114</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.6125</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.5489</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.1329</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2392</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5783</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8755</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5479</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.3991</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2417</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8679</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6482</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.6718</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.2888</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.2533</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.2543</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.7492</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.2309</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="n">
-        <v>-0.3181</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.2973</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2846</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.7275</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.4062</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.3029</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="n">
-        <v>-0.7947</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2635</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.4517</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.2695</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.7571</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.1406</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.2384</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5555</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.1509</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7212</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.8366</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="n">
-        <v>-0.1911</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.3592</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5947</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.4085</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.6701</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="n">
-        <v>-0.3377</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.5081</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.5063</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.7134</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2636</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.9312</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.292</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5321</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5832</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.7468</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2632</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.1189</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.2599</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.5222</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.6188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.7712</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.2771</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.1462</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="n">
-        <v>-0.3529</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4822</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.7027</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2627</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.8797</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="n">
-        <v>-0.4626</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4881</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3433</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6297</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.2419</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.6391</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="n">
-        <v>-0.5216</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.4803</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2774</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.5935</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.2316</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.5214</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" t="n">
-        <v>-0.5281</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2722</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.5897</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.2297</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.5139</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" t="n">
-        <v>-0.556</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.4993</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.2655</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.5735</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.2156</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.526</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" t="n">
-        <v>-0.4393</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.5104</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.3893</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.6445</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.7524</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" t="n">
-        <v>-0.2169</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.5292</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.6818</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.2853</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.271</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.6781</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.0068</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.2665</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3.8036</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" t="n">
-        <v>-0.2728</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.7612</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.6598</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.8783</v>
+        <v>0.739</v>
       </c>
     </row>
   </sheetData>
